--- a/info/flowcharts and schemas/database/schema_x_tables.xlsx
+++ b/info/flowcharts and schemas/database/schema_x_tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Quality Management KD Brugge\00_CODE\klaw32project\info\flowcharts and schemas\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E187F274-3DF8-420F-8E68-243D2C38088A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC2903C-2144-4A21-B3AE-A41ADCAE6C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{250840B8-A0D8-439D-9982-F22A3BE79632}"/>
   </bookViews>
@@ -39,40 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
-  <si>
-    <t>claims</t>
-  </si>
-  <si>
-    <t>hr</t>
-  </si>
-  <si>
-    <t>inventory</t>
-  </si>
-  <si>
-    <t>logistics</t>
-  </si>
-  <si>
-    <t>maintenance</t>
-  </si>
-  <si>
-    <t>master_data</t>
-  </si>
-  <si>
-    <t>procurement</t>
-  </si>
-  <si>
-    <t>product</t>
-  </si>
-  <si>
-    <t>production</t>
-  </si>
-  <si>
-    <t>quality</t>
-  </si>
-  <si>
-    <t>sales</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>customer</t>
   </si>
@@ -86,15 +53,6 @@
     <t>postal_location</t>
   </si>
   <si>
-    <t>transport</t>
-  </si>
-  <si>
-    <t>transport_planning</t>
-  </si>
-  <si>
-    <t>reference</t>
-  </si>
-  <si>
     <t>unit</t>
   </si>
   <si>
@@ -171,6 +129,93 @@
   </si>
   <si>
     <t>blocking_task</t>
+  </si>
+  <si>
+    <t>frequency_type</t>
+  </si>
+  <si>
+    <t>carrier</t>
+  </si>
+  <si>
+    <t>shipment</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>event_type</t>
+  </si>
+  <si>
+    <t>assignment</t>
+  </si>
+  <si>
+    <t>schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> logistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> maintenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> master_data</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> procurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> product</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> production</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> sales</t>
+  </si>
+  <si>
+    <t>resource</t>
+  </si>
+  <si>
+    <t>resource_type</t>
+  </si>
+  <si>
+    <t>resource_component</t>
+  </si>
+  <si>
+    <t>resource_capability</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>location_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> claim</t>
+  </si>
+  <si>
+    <t>internal_product</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> warehouse</t>
   </si>
 </sst>
 </file>
@@ -202,7 +247,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -210,18 +255,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -229,6 +287,9 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
+      <font>
+        <color theme="6" tint="0.39994506668294322"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
@@ -589,317 +650,416 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB921535-F53B-4C04-85AF-74C80CB26FA7}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="5.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="15" width="5.140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="5.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="66.75" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:16" ht="68.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="O9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="O10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="O11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="L22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="L26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="L27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="L28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="L29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="L30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="L31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="L32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="L33" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="L34" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J21" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="N35" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="G36" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="G37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J26" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="G38" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J27" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J28" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J29" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J31" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J34" s="3">
+      <c r="G39" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I42" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I43" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:M70">
+  <conditionalFormatting sqref="B2:P70">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="notEqual">
       <formula>1</formula>
     </cfRule>
